--- a/NR_dataset.xlsx
+++ b/NR_dataset.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://purdue0-my.sharepoint.com/personal/gonz1400_purdue_edu/Documents/Desktop/JIGE/JIGE/PURDUE/SPRING 2026/MGMT 389 AI for Business Analytics/CHALLENGES/CHALLENGE 1/CASE NOVARETAIL/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\liald\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{54BEEB3F-E483-4E63-9A48-CDEABBD3AAD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5443B1D3-3BF7-47CD-B517-417596C9F8B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{93A87C8B-4E0A-4F73-8141-ECE95F98B4F8}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{93A87C8B-4E0A-4F73-8141-ECE95F98B4F8}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="711" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="705" uniqueCount="89">
   <si>
     <t>idx</t>
   </si>
@@ -284,9 +284,6 @@
   </si>
   <si>
     <t>TX1015</t>
-  </si>
-  <si>
-    <t>TX2010</t>
   </si>
   <si>
     <t>Outdoor Equipment</t>
@@ -1151,24 +1148,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0533E387-F155-4251-A5DA-51E73CE265D2}">
-  <dimension ref="A1:L101"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:L100"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="16.36328125" customWidth="1"/>
-    <col min="2" max="2" width="27.6328125" customWidth="1"/>
-    <col min="3" max="3" width="10.54296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.90625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.36328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.81640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.81640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.81640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.81640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.36328125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="22.7265625" customWidth="1"/>
-    <col min="12" max="12" width="19.26953125" customWidth="1"/>
+    <col min="1" max="1" width="16.33203125" customWidth="1"/>
+    <col min="2" max="2" width="27.59765625" customWidth="1"/>
+    <col min="3" max="3" width="10.53125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.9296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.796875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.796875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.796875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.796875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="22.73046875" customWidth="1"/>
+    <col min="12" max="12" width="19.265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1206,7 +1203,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A2">
         <v>0</v>
       </c>
@@ -1244,7 +1241,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1282,7 +1279,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A4">
         <v>2</v>
       </c>
@@ -1320,7 +1317,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A5">
         <v>3</v>
       </c>
@@ -1358,7 +1355,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A6">
         <v>4</v>
       </c>
@@ -1396,7 +1393,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A7">
         <v>5</v>
       </c>
@@ -1434,7 +1431,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A8">
         <v>6</v>
       </c>
@@ -1472,7 +1469,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A9">
         <v>7</v>
       </c>
@@ -1510,7 +1507,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A10">
         <v>8</v>
       </c>
@@ -1548,7 +1545,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A11">
         <v>9</v>
       </c>
@@ -1586,7 +1583,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A12">
         <v>10</v>
       </c>
@@ -1624,7 +1621,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A13">
         <v>11</v>
       </c>
@@ -1662,7 +1659,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A14">
         <v>12</v>
       </c>
@@ -1700,7 +1697,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A15">
         <v>13</v>
       </c>
@@ -1738,7 +1735,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A16">
         <v>14</v>
       </c>
@@ -1776,7 +1773,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A17">
         <v>15</v>
       </c>
@@ -1814,7 +1811,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A18">
         <v>16</v>
       </c>
@@ -1852,7 +1849,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A19">
         <v>17</v>
       </c>
@@ -1890,7 +1887,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A20">
         <v>18</v>
       </c>
@@ -1928,7 +1925,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A21">
         <v>19</v>
       </c>
@@ -1966,7 +1963,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A22">
         <v>20</v>
       </c>
@@ -2004,7 +2001,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A23">
         <v>21</v>
       </c>
@@ -2042,7 +2039,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A24">
         <v>22</v>
       </c>
@@ -2080,7 +2077,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A25">
         <v>23</v>
       </c>
@@ -2118,7 +2115,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A26">
         <v>24</v>
       </c>
@@ -2156,7 +2153,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A27">
         <v>25</v>
       </c>
@@ -2194,7 +2191,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A28">
         <v>26</v>
       </c>
@@ -2232,7 +2229,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A29">
         <v>27</v>
       </c>
@@ -2270,7 +2267,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A30">
         <v>28</v>
       </c>
@@ -2308,7 +2305,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A31">
         <v>29</v>
       </c>
@@ -2346,7 +2343,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A32">
         <v>30</v>
       </c>
@@ -2384,7 +2381,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A33">
         <v>31</v>
       </c>
@@ -2422,7 +2419,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A34">
         <v>32</v>
       </c>
@@ -2460,7 +2457,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A35">
         <v>33</v>
       </c>
@@ -2498,7 +2495,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A36">
         <v>34</v>
       </c>
@@ -2536,7 +2533,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A37">
         <v>35</v>
       </c>
@@ -2574,7 +2571,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A38">
         <v>36</v>
       </c>
@@ -2612,7 +2609,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A39">
         <v>37</v>
       </c>
@@ -2650,7 +2647,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A40">
         <v>38</v>
       </c>
@@ -2688,7 +2685,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A41">
         <v>39</v>
       </c>
@@ -2726,7 +2723,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A42">
         <v>40</v>
       </c>
@@ -2764,7 +2761,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A43">
         <v>41</v>
       </c>
@@ -2802,7 +2799,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A44">
         <v>42</v>
       </c>
@@ -2840,7 +2837,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A45">
         <v>43</v>
       </c>
@@ -2878,7 +2875,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A46">
         <v>44</v>
       </c>
@@ -2916,7 +2913,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A47">
         <v>45</v>
       </c>
@@ -2954,7 +2951,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A48">
         <v>46</v>
       </c>
@@ -2992,7 +2989,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A49">
         <v>47</v>
       </c>
@@ -3030,7 +3027,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A50">
         <v>48</v>
       </c>
@@ -3068,7 +3065,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A51">
         <v>49</v>
       </c>
@@ -3106,7 +3103,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A52">
         <v>50</v>
       </c>
@@ -3144,7 +3141,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A53">
         <v>51</v>
       </c>
@@ -3182,7 +3179,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A54">
         <v>52</v>
       </c>
@@ -3220,7 +3217,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A55">
         <v>53</v>
       </c>
@@ -3258,7 +3255,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A56">
         <v>54</v>
       </c>
@@ -3296,7 +3293,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A57">
         <v>55</v>
       </c>
@@ -3334,7 +3331,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A58">
         <v>56</v>
       </c>
@@ -3372,7 +3369,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A59">
         <v>57</v>
       </c>
@@ -3410,7 +3407,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A60">
         <v>58</v>
       </c>
@@ -3448,7 +3445,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A61">
         <v>59</v>
       </c>
@@ -3486,7 +3483,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A62">
         <v>60</v>
       </c>
@@ -3524,7 +3521,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A63">
         <v>61</v>
       </c>
@@ -3562,7 +3559,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A64">
         <v>62</v>
       </c>
@@ -3600,7 +3597,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A65">
         <v>63</v>
       </c>
@@ -3638,7 +3635,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A66">
         <v>64</v>
       </c>
@@ -3676,7 +3673,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A67">
         <v>65</v>
       </c>
@@ -3714,7 +3711,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A68">
         <v>66</v>
       </c>
@@ -3752,7 +3749,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A69">
         <v>67</v>
       </c>
@@ -3790,7 +3787,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A70">
         <v>68</v>
       </c>
@@ -3828,7 +3825,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A71">
         <v>69</v>
       </c>
@@ -3866,7 +3863,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A72">
         <v>70</v>
       </c>
@@ -3904,7 +3901,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A73">
         <v>71</v>
       </c>
@@ -3942,7 +3939,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A74">
         <v>72</v>
       </c>
@@ -3980,7 +3977,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A75">
         <v>73</v>
       </c>
@@ -4018,7 +4015,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A76">
         <v>74</v>
       </c>
@@ -4056,7 +4053,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A77">
         <v>75</v>
       </c>
@@ -4094,7 +4091,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A78">
         <v>76</v>
       </c>
@@ -4132,7 +4129,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A79">
         <v>77</v>
       </c>
@@ -4170,7 +4167,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A80">
         <v>78</v>
       </c>
@@ -4208,7 +4205,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A81">
         <v>79</v>
       </c>
@@ -4246,7 +4243,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A82">
         <v>80</v>
       </c>
@@ -4284,7 +4281,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A83">
         <v>81</v>
       </c>
@@ -4322,7 +4319,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A84">
         <v>82</v>
       </c>
@@ -4360,7 +4357,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A85">
         <v>83</v>
       </c>
@@ -4398,7 +4395,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A86">
         <v>84</v>
       </c>
@@ -4436,7 +4433,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A87">
         <v>85</v>
       </c>
@@ -4474,7 +4471,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A88">
         <v>86</v>
       </c>
@@ -4512,7 +4509,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A89">
         <v>87</v>
       </c>
@@ -4550,7 +4547,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A90">
         <v>88</v>
       </c>
@@ -4588,7 +4585,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A91">
         <v>89</v>
       </c>
@@ -4626,7 +4623,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A92">
         <v>90</v>
       </c>
@@ -4664,7 +4661,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A93">
         <v>91</v>
       </c>
@@ -4702,7 +4699,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A94">
         <v>92</v>
       </c>
@@ -4740,7 +4737,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A95">
         <v>93</v>
       </c>
@@ -4778,7 +4775,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A96">
         <v>94</v>
       </c>
@@ -4816,7 +4813,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A97">
         <v>95</v>
       </c>
@@ -4854,7 +4851,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A98">
         <v>96</v>
       </c>
@@ -4892,47 +4889,50 @@
         <v>18</v>
       </c>
     </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A99">
-        <v>97</v>
+        <v>98</v>
+      </c>
+      <c r="B99" t="s">
+        <v>35</v>
       </c>
       <c r="C99">
-        <v>12509</v>
+        <v>12359</v>
       </c>
       <c r="D99" t="s">
+        <v>87</v>
+      </c>
+      <c r="E99" s="1">
+        <v>44955</v>
+      </c>
+      <c r="F99" t="s">
         <v>88</v>
       </c>
-      <c r="E99" s="1">
-        <v>44957</v>
-      </c>
-      <c r="F99" t="s">
-        <v>89</v>
-      </c>
       <c r="G99">
-        <v>249.99</v>
+        <v>24.99</v>
       </c>
       <c r="H99" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="I99" t="s">
         <v>16</v>
       </c>
       <c r="J99" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="K99">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L99" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A100">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B100" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="C100">
         <v>12359</v>
@@ -4941,65 +4941,27 @@
         <v>87</v>
       </c>
       <c r="E100" s="1">
-        <v>44955</v>
+        <v>44967</v>
       </c>
       <c r="F100" t="s">
-        <v>89</v>
+        <v>37</v>
       </c>
       <c r="G100">
-        <v>24.99</v>
+        <v>39.99</v>
       </c>
       <c r="H100" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="I100" t="s">
         <v>16</v>
       </c>
       <c r="J100" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="K100">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L100" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A101">
-        <v>99</v>
-      </c>
-      <c r="B101" t="s">
-        <v>12</v>
-      </c>
-      <c r="C101">
-        <v>12359</v>
-      </c>
-      <c r="D101" t="s">
-        <v>87</v>
-      </c>
-      <c r="E101" s="1">
-        <v>44967</v>
-      </c>
-      <c r="F101" t="s">
-        <v>37</v>
-      </c>
-      <c r="G101">
-        <v>39.99</v>
-      </c>
-      <c r="H101" t="s">
-        <v>15</v>
-      </c>
-      <c r="I101" t="s">
-        <v>16</v>
-      </c>
-      <c r="J101" t="s">
-        <v>29</v>
-      </c>
-      <c r="K101">
-        <v>5</v>
-      </c>
-      <c r="L101" t="s">
         <v>25</v>
       </c>
     </row>
